--- a/Prak6/testCaseImplementasi.xlsx
+++ b/Prak6/testCaseImplementasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M. Syafiq Romadhon\Documents\GitHub\PraktikumStrukdatGenap2526\Prak6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D606A76-07E8-473B-8BFA-A74091144C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C241629-7710-413B-A5CA-F003065F6DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{328E3CF4-D241-4823-A045-42CCF51E3869}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Data acak</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>insertion sort linked list</t>
+  </si>
+  <si>
+    <t>best case</t>
+  </si>
+  <si>
+    <t>worst case</t>
+  </si>
+  <si>
+    <t>O(n2)</t>
+  </si>
+  <si>
+    <t>O(n)</t>
   </si>
 </sst>
 </file>
@@ -233,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -241,17 +253,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -260,19 +283,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -589,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6166CC2E-23A8-4AE3-83FC-EDBE34D9A14F}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
@@ -610,274 +620,254 @@
     <col min="16" max="16" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="4" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="5" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>31</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>22</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="6">
         <f>SUM(D3,E3)</f>
         <v>53</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="3">
         <v>45</v>
       </c>
-      <c r="H3" s="6">
-        <v>2</v>
-      </c>
-      <c r="I3" s="15">
+      <c r="H3" s="3">
+        <v>4</v>
+      </c>
+      <c r="I3" s="6">
         <f>SUM(G3,H3)</f>
-        <v>47</v>
-      </c>
-      <c r="J3" s="15">
+        <v>49</v>
+      </c>
+      <c r="J3" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="4">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6">
-        <v>117</v>
-      </c>
-      <c r="E4" s="6">
-        <v>100</v>
-      </c>
-      <c r="F4" s="15">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="6">
         <f t="shared" ref="F4:F10" si="0">SUM(D4,E4)</f>
-        <v>217</v>
-      </c>
-      <c r="G4" s="6">
-        <v>190</v>
-      </c>
-      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="6">
+        <f t="shared" ref="I4:I10" si="1">SUM(G4,H4)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
+      <c r="B6" s="4">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="15">
-        <f t="shared" ref="I3:I10" si="1">SUM(G4,H4)</f>
-        <v>208</v>
-      </c>
-      <c r="J4" s="15">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4">
         <v>10</v>
       </c>
-      <c r="B5" s="5">
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="4">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6">
-        <v>5</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G5" s="6">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6">
-        <v>5</v>
-      </c>
-      <c r="I5" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="6">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="J5" s="15">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="4">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="15">
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="15">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="5">
-        <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="5">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -885,8 +875,6 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -894,7 +882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863F2767-E304-4BAC-9BD3-5B9743B6F86B}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
@@ -915,347 +903,375 @@
     <col min="16" max="16" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="4" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="5" t="s">
+    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>19</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>11</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="5">
         <f>SUM(D3,E3)</f>
         <v>30</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>45</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>7</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="5">
         <f>SUM(G3,H3)</f>
         <v>52</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="4">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>117</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>100</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="5">
         <f t="shared" ref="F4:F10" si="0">SUM(D4,E4)</f>
         <v>217</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>190</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>18</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="5">
         <f t="shared" ref="I4:I10" si="1">SUM(G4,H4)</f>
         <v>208</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="5">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>14</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>5</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>45</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>5</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="5">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
+      <c r="B6" s="4">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>56</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>37</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>190</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>9</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="5">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="5">
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>9</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>45</v>
       </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14">
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="5">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="4">
         <v>20</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>19</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>190</v>
       </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14">
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="5">
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>45</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>45</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>45</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>5</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="5">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="5">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="4">
         <v>20</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>190</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>190</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>190</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>10</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="5">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="F11" s="16">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F11" s="7">
         <f>AVERAGE(F3:F10)</f>
         <v>107.125</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="7">
         <f>AVERAGE(I3:I10)</f>
         <v>124.25</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="7">
         <f>AVERAGE(J3:J10)</f>
         <v>62.125</v>
       </c>
     </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
